--- a/results/5153_bef_gauss.xlsx
+++ b/results/5153_bef_gauss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,185 +435,557 @@
         </is>
       </c>
       <c r="B1" s="1" t="n">
-        <v>-1.0385</v>
+        <v>-2.387</v>
       </c>
       <c r="C1" s="1" t="n">
-        <v>-0.9299999999999999</v>
+        <v>-2.1235</v>
       </c>
       <c r="D1" s="1" t="n">
-        <v>-0.8215</v>
+        <v>-1.86</v>
       </c>
       <c r="E1" s="1" t="n">
-        <v>-0.6975</v>
+        <v>-1.5965</v>
       </c>
       <c r="F1" s="1" t="n">
-        <v>-0.589</v>
+        <v>-1.333</v>
       </c>
       <c r="G1" s="1" t="n">
-        <v>-0.465</v>
+        <v>-1.0695</v>
       </c>
       <c r="H1" s="1" t="n">
-        <v>-0.3565</v>
+        <v>-0.806</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>-0.2325</v>
+        <v>-0.5425</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>-0.124</v>
+        <v>-0.279</v>
       </c>
       <c r="K1" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.093</v>
+        <v>0.217</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>0.2015</v>
+        <v>0.4495</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>0.31</v>
+        <v>0.6819999999999999</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>0.403</v>
+        <v>0.9145</v>
       </c>
       <c r="P1" s="1" t="n">
-        <v>0.5115</v>
+        <v>1.147</v>
       </c>
       <c r="Q1" s="1" t="n">
-        <v>0.62</v>
+        <v>1.3795</v>
       </c>
       <c r="R1" s="1" t="n">
-        <v>0.713</v>
+        <v>1.612</v>
       </c>
       <c r="S1" s="1" t="n">
-        <v>0.8215</v>
+        <v>1.8445</v>
       </c>
       <c r="T1" s="1" t="n">
-        <v>0.9299999999999999</v>
+        <v>2.077</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>515.2894700000001</v>
+        <v>514.91045</v>
       </c>
       <c r="B2" t="n">
-        <v>21.8429613396691</v>
+        <v>-3.51555025039963</v>
       </c>
       <c r="C2" t="n">
-        <v>26.09585655330656</v>
+        <v>-4.11675379989269</v>
       </c>
       <c r="D2" t="n">
-        <v>30.71738845801845</v>
+        <v>-3.504872659703404</v>
       </c>
       <c r="E2" t="n">
-        <v>35.38609307417983</v>
+        <v>-0.09732516189377614</v>
       </c>
       <c r="F2" t="n">
-        <v>39.14066764932924</v>
+        <v>8.268795890865469</v>
       </c>
       <c r="G2" t="n">
-        <v>42.78563749762619</v>
+        <v>17.92042291117859</v>
       </c>
       <c r="H2" t="n">
-        <v>46.01262127023795</v>
+        <v>27.72294308916804</v>
       </c>
       <c r="I2" t="n">
-        <v>48.61950071969012</v>
+        <v>37.47034474313969</v>
       </c>
       <c r="J2" t="n">
-        <v>49.31994746367838</v>
+        <v>47.52507467029977</v>
       </c>
       <c r="K2" t="n">
-        <v>50.30748128869072</v>
+        <v>52.50478893002047</v>
       </c>
       <c r="L2" t="n">
-        <v>49.72483421026646</v>
+        <v>51.77625513607089</v>
       </c>
       <c r="M2" t="n">
-        <v>47.94807170067094</v>
+        <v>45.06793604741387</v>
       </c>
       <c r="N2" t="n">
-        <v>45.80573614783044</v>
+        <v>34.9750892957496</v>
       </c>
       <c r="O2" t="n">
-        <v>43.37860412850207</v>
+        <v>23.85657893867744</v>
       </c>
       <c r="P2" t="n">
-        <v>40.12767695111589</v>
+        <v>14.44886693177896</v>
       </c>
       <c r="Q2" t="n">
-        <v>36.7046580252933</v>
+        <v>5.393406211869743</v>
       </c>
       <c r="R2" t="n">
-        <v>34.30871254606946</v>
+        <v>-1.3143274933482</v>
       </c>
       <c r="S2" t="n">
-        <v>30.80446520700326</v>
+        <v>-4.144149744841276</v>
       </c>
       <c r="T2" t="n">
-        <v>26.65647463850485</v>
+        <v>-3.375172350196925</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>515.00522</v>
+      </c>
+      <c r="B3" t="n">
+        <v>15.0530600505775</v>
+      </c>
+      <c r="C3" t="n">
+        <v>35.09222881883489</v>
+      </c>
+      <c r="D3" t="n">
+        <v>81.4885458084164</v>
+      </c>
+      <c r="E3" t="n">
+        <v>167.9899723167611</v>
+      </c>
+      <c r="F3" t="n">
+        <v>308.4055960523193</v>
+      </c>
+      <c r="G3" t="n">
+        <v>493.3047926527788</v>
+      </c>
+      <c r="H3" t="n">
+        <v>695.3352657042399</v>
+      </c>
+      <c r="I3" t="n">
+        <v>873.880298414392</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1005.271377848337</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1062.658256953558</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1037.58936393795</v>
+      </c>
+      <c r="M3" t="n">
+        <v>944.6000875869706</v>
+      </c>
+      <c r="N3" t="n">
+        <v>798.9850697095156</v>
+      </c>
+      <c r="O3" t="n">
+        <v>617.895824959907</v>
+      </c>
+      <c r="P3" t="n">
+        <v>431.9022115437058</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>266.3471185794246</v>
+      </c>
+      <c r="R3" t="n">
+        <v>139.3605039439806</v>
+      </c>
+      <c r="S3" t="n">
+        <v>61.20180598449065</v>
+      </c>
+      <c r="T3" t="n">
+        <v>22.9582003530173</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>515.09997</v>
+      </c>
+      <c r="B4" t="n">
+        <v>72.5215838857095</v>
+      </c>
+      <c r="C4" t="n">
+        <v>163.9395465971124</v>
+      </c>
+      <c r="D4" t="n">
+        <v>323.3237316123626</v>
+      </c>
+      <c r="E4" t="n">
+        <v>568.6246769411269</v>
+      </c>
+      <c r="F4" t="n">
+        <v>879.8434764637426</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1228.66829317619</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1569.256677641939</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1855.368134618961</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2034.788960745785</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2089.880592903292</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2031.421800451971</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1880.314288975173</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1635.543597505471</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1321.330638180703</v>
+      </c>
+      <c r="P4" t="n">
+        <v>977.0596277883957</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>646.370589304182</v>
+      </c>
+      <c r="R4" t="n">
+        <v>373.5592540666884</v>
+      </c>
+      <c r="S4" t="n">
+        <v>179.4424072253527</v>
+      </c>
+      <c r="T4" t="n">
+        <v>70.28645861204309</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>515.19472</v>
+      </c>
+      <c r="B5" t="n">
+        <v>33.54087601016531</v>
+      </c>
+      <c r="C5" t="n">
+        <v>55.11492096921103</v>
+      </c>
+      <c r="D5" t="n">
+        <v>86.70241889717992</v>
+      </c>
+      <c r="E5" t="n">
+        <v>131.2555527601817</v>
+      </c>
+      <c r="F5" t="n">
+        <v>182.8129599793673</v>
+      </c>
+      <c r="G5" t="n">
+        <v>234.797351163833</v>
+      </c>
+      <c r="H5" t="n">
+        <v>284.8483691584034</v>
+      </c>
+      <c r="I5" t="n">
+        <v>331.7502126041914</v>
+      </c>
+      <c r="J5" t="n">
+        <v>361.2878488426022</v>
+      </c>
+      <c r="K5" t="n">
+        <v>371.5078604813737</v>
+      </c>
+      <c r="L5" t="n">
+        <v>364.2970009382957</v>
+      </c>
+      <c r="M5" t="n">
+        <v>348.2078599272111</v>
+      </c>
+      <c r="N5" t="n">
+        <v>317.414989420521</v>
+      </c>
+      <c r="O5" t="n">
+        <v>275.0558603777755</v>
+      </c>
+      <c r="P5" t="n">
+        <v>218.1510430437585</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>157.5557132325692</v>
+      </c>
+      <c r="R5" t="n">
+        <v>99.703511528486</v>
+      </c>
+      <c r="S5" t="n">
+        <v>55.73409872367706</v>
+      </c>
+      <c r="T5" t="n">
+        <v>27.29912554481753</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>515.2894700000001</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-1.87904060959318</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-2.206236036824766</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1432478822893087</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.91393886923853</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12.83451559039491</v>
+      </c>
+      <c r="G6" t="n">
+        <v>23.79952923232909</v>
+      </c>
+      <c r="H6" t="n">
+        <v>34.26409467527549</v>
+      </c>
+      <c r="I6" t="n">
+        <v>42.78563749762619</v>
+      </c>
+      <c r="J6" t="n">
+        <v>48.94431909410113</v>
+      </c>
+      <c r="K6" t="n">
+        <v>49.9490845875561</v>
+      </c>
+      <c r="L6" t="n">
+        <v>46.17140348738564</v>
+      </c>
+      <c r="M6" t="n">
+        <v>39.60034448117814</v>
+      </c>
+      <c r="N6" t="n">
+        <v>33.0811769309449</v>
+      </c>
+      <c r="O6" t="n">
+        <v>25.00104495934754</v>
+      </c>
+      <c r="P6" t="n">
+        <v>17.18405764625303</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>9.574110651576644</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.280087329073857</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.3543645516187205</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1.320725908223081</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>515.3842</v>
       </c>
-      <c r="B3" t="n">
-        <v>17.37730487743349</v>
-      </c>
-      <c r="C3" t="n">
-        <v>19.04726712348721</v>
-      </c>
-      <c r="D3" t="n">
-        <v>20.9261885748099</v>
-      </c>
-      <c r="E3" t="n">
-        <v>22.31625164538217</v>
-      </c>
-      <c r="F3" t="n">
-        <v>23.43971396201703</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="B7" t="n">
+        <v>1.135555004152329</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.197414192362372</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.298247910953368</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.87017801636892</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13.73608728581745</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18.16091907988385</v>
+      </c>
+      <c r="H7" t="n">
+        <v>21.9660438408764</v>
+      </c>
+      <c r="I7" t="n">
         <v>24.25895132099721</v>
       </c>
-      <c r="H3" t="n">
-        <v>24.58057792698513</v>
-      </c>
-      <c r="I3" t="n">
-        <v>24.81487423857012</v>
-      </c>
-      <c r="J3" t="n">
-        <v>24.5886567377105</v>
-      </c>
-      <c r="K3" t="n">
-        <v>24.46522315327696</v>
-      </c>
-      <c r="L3" t="n">
-        <v>23.97787390379596</v>
-      </c>
-      <c r="M3" t="n">
-        <v>22.76021901660851</v>
-      </c>
-      <c r="N3" t="n">
-        <v>21.26817127024342</v>
-      </c>
-      <c r="O3" t="n">
-        <v>19.9385824378076</v>
-      </c>
-      <c r="P3" t="n">
-        <v>18.45838387567122</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>17.09829429258237</v>
-      </c>
-      <c r="R3" t="n">
-        <v>15.94833135593319</v>
-      </c>
-      <c r="S3" t="n">
-        <v>14.78134479016919</v>
-      </c>
-      <c r="T3" t="n">
-        <v>12.98747569925781</v>
+      <c r="J7" t="n">
+        <v>24.78231647424796</v>
+      </c>
+      <c r="K7" t="n">
+        <v>24.13072720210462</v>
+      </c>
+      <c r="L7" t="n">
+        <v>21.4827271236814</v>
+      </c>
+      <c r="M7" t="n">
+        <v>18.27918901998041</v>
+      </c>
+      <c r="N7" t="n">
+        <v>15.43384425404108</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12.09616333054173</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8.873176383519368</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.857258545673806</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.907538513144994</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.473585938510466</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.285661035517669</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>515.47894</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1.209615984804993</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.549573540344215</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.545729151110853</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.951486689690981</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.603227821317624</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.889729630365473</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.418038215579486</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10.06513723979669</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11.10690702842374</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11.21910781484931</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10.45592925807757</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9.432108493341746</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7.618121339521275</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.712690853976025</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.852437722904174</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.608176244568031</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.435354531708073</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5901248368452088</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.3282997700466189</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>515.57366</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1296941118225361</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1851708632497856</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5584703433200073</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.464755644314121</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.631647759502965</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.803215223309122</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.751822772113981</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.285963570210944</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.630430700235451</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8.063934239561121</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.655616212078352</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6.682606461043768</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.150655792703795</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.770897574500202</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.700526065889048</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.788884064361279</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.135285229170351</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.5486569149997491</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.318665840366791</v>
       </c>
     </row>
   </sheetData>

--- a/results/5153_bef_gauss.xlsx
+++ b/results/5153_bef_gauss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,557 +435,1053 @@
         </is>
       </c>
       <c r="B1" s="1" t="n">
-        <v>-2.387</v>
+        <v>-2.976</v>
       </c>
       <c r="C1" s="1" t="n">
-        <v>-2.1235</v>
+        <v>-2.6505</v>
       </c>
       <c r="D1" s="1" t="n">
-        <v>-1.86</v>
+        <v>-2.325</v>
       </c>
       <c r="E1" s="1" t="n">
-        <v>-1.5965</v>
+        <v>-1.984</v>
       </c>
       <c r="F1" s="1" t="n">
+        <v>-1.6585</v>
+      </c>
+      <c r="G1" s="1" t="n">
         <v>-1.333</v>
       </c>
-      <c r="G1" s="1" t="n">
-        <v>-1.0695</v>
-      </c>
       <c r="H1" s="1" t="n">
-        <v>-0.806</v>
+        <v>-0.992</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>-0.5425</v>
+        <v>-0.6665</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>-0.279</v>
+        <v>-0.341</v>
       </c>
       <c r="K1" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.217</v>
+        <v>0.3255</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>0.4495</v>
+        <v>0.651</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.992</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>0.9145</v>
+        <v>1.3175</v>
       </c>
       <c r="P1" s="1" t="n">
-        <v>1.147</v>
+        <v>1.6585</v>
       </c>
       <c r="Q1" s="1" t="n">
-        <v>1.3795</v>
+        <v>1.984</v>
       </c>
       <c r="R1" s="1" t="n">
-        <v>1.612</v>
+        <v>2.325</v>
       </c>
       <c r="S1" s="1" t="n">
-        <v>1.8445</v>
+        <v>2.6505</v>
       </c>
       <c r="T1" s="1" t="n">
-        <v>2.077</v>
+        <v>2.9915</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>514.91045</v>
+        <v>514.504</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.51555025039963</v>
+        <v>0.02983447713218064</v>
       </c>
       <c r="C2" t="n">
-        <v>-4.11675379989269</v>
+        <v>0.03828301127912895</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.504872659703404</v>
+        <v>0.04734178773171677</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.09732516189377614</v>
+        <v>0.04643630496352613</v>
       </c>
       <c r="F2" t="n">
-        <v>8.268795890865469</v>
+        <v>0.04825290483543493</v>
       </c>
       <c r="G2" t="n">
-        <v>17.92042291117859</v>
+        <v>0.08734902492082604</v>
       </c>
       <c r="H2" t="n">
-        <v>27.72294308916804</v>
+        <v>0.1021966201672224</v>
       </c>
       <c r="I2" t="n">
-        <v>37.47034474313969</v>
+        <v>0.1394202113004699</v>
       </c>
       <c r="J2" t="n">
-        <v>47.52507467029977</v>
+        <v>0.1776785658494796</v>
       </c>
       <c r="K2" t="n">
-        <v>52.50478893002047</v>
+        <v>0.1768072894146817</v>
       </c>
       <c r="L2" t="n">
-        <v>51.77625513607089</v>
+        <v>0.1849277189325604</v>
       </c>
       <c r="M2" t="n">
-        <v>45.06793604741387</v>
+        <v>0.2009801626472007</v>
       </c>
       <c r="N2" t="n">
-        <v>34.9750892957496</v>
+        <v>0.2070252698879047</v>
       </c>
       <c r="O2" t="n">
-        <v>23.85657893867744</v>
+        <v>0.1656438923963583</v>
       </c>
       <c r="P2" t="n">
-        <v>14.44886693177896</v>
+        <v>0.1164535374274953</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.393406211869743</v>
+        <v>0.07221892622664464</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.3143274933482</v>
+        <v>0.03909793317914669</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.144149744841276</v>
+        <v>0.02843696359366446</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.375172350196925</v>
+        <v>0.01333504888809721</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>515.00522</v>
+        <v>514.6004</v>
       </c>
       <c r="B3" t="n">
-        <v>15.0530600505775</v>
+        <v>0.01820676552214772</v>
       </c>
       <c r="C3" t="n">
-        <v>35.09222881883489</v>
+        <v>0.02425760824764095</v>
       </c>
       <c r="D3" t="n">
-        <v>81.4885458084164</v>
+        <v>0.03326278605941754</v>
       </c>
       <c r="E3" t="n">
-        <v>167.9899723167611</v>
+        <v>0.04897449664472146</v>
       </c>
       <c r="F3" t="n">
-        <v>308.4055960523193</v>
+        <v>0.06149027945916635</v>
       </c>
       <c r="G3" t="n">
-        <v>493.3047926527788</v>
+        <v>0.07901836056928777</v>
       </c>
       <c r="H3" t="n">
-        <v>695.3352657042399</v>
+        <v>0.0652570248425498</v>
       </c>
       <c r="I3" t="n">
-        <v>873.880298414392</v>
+        <v>0.07096553934886497</v>
       </c>
       <c r="J3" t="n">
-        <v>1005.271377848337</v>
+        <v>0.09814997839529596</v>
       </c>
       <c r="K3" t="n">
-        <v>1062.658256953558</v>
+        <v>0.1349943164703688</v>
       </c>
       <c r="L3" t="n">
-        <v>1037.58936393795</v>
+        <v>0.1342712776231886</v>
       </c>
       <c r="M3" t="n">
-        <v>944.6000875869706</v>
+        <v>0.1096427387297551</v>
       </c>
       <c r="N3" t="n">
-        <v>798.9850697095156</v>
+        <v>0.1111065888489509</v>
       </c>
       <c r="O3" t="n">
-        <v>617.895824959907</v>
+        <v>0.1171657437751202</v>
       </c>
       <c r="P3" t="n">
-        <v>431.9022115437058</v>
+        <v>0.09016623928837607</v>
       </c>
       <c r="Q3" t="n">
-        <v>266.3471185794246</v>
+        <v>0.05678257870841062</v>
       </c>
       <c r="R3" t="n">
-        <v>139.3605039439806</v>
+        <v>0.04012020873865558</v>
       </c>
       <c r="S3" t="n">
-        <v>61.20180598449065</v>
+        <v>0.02911075339619067</v>
       </c>
       <c r="T3" t="n">
-        <v>22.9582003530173</v>
+        <v>0.02852850996619604</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>515.09997</v>
+        <v>514.6968000000001</v>
       </c>
       <c r="B4" t="n">
-        <v>72.5215838857095</v>
+        <v>0.02247391568048221</v>
       </c>
       <c r="C4" t="n">
-        <v>163.9395465971124</v>
+        <v>0.01809284382138274</v>
       </c>
       <c r="D4" t="n">
-        <v>323.3237316123626</v>
+        <v>0.01940114838640665</v>
       </c>
       <c r="E4" t="n">
-        <v>568.6246769411269</v>
+        <v>0.02570564196406141</v>
       </c>
       <c r="F4" t="n">
-        <v>879.8434764637426</v>
+        <v>0.03759915222202172</v>
       </c>
       <c r="G4" t="n">
-        <v>1228.66829317619</v>
+        <v>0.0434947242768158</v>
       </c>
       <c r="H4" t="n">
-        <v>1569.256677641939</v>
+        <v>0.05806270681372985</v>
       </c>
       <c r="I4" t="n">
-        <v>1855.368134618961</v>
+        <v>0.06930587249955003</v>
       </c>
       <c r="J4" t="n">
-        <v>2034.788960745785</v>
+        <v>0.07631438677814763</v>
       </c>
       <c r="K4" t="n">
-        <v>2089.880592903292</v>
+        <v>0.08057092744350933</v>
       </c>
       <c r="L4" t="n">
-        <v>2031.421800451971</v>
+        <v>0.09244618109232537</v>
       </c>
       <c r="M4" t="n">
-        <v>1880.314288975173</v>
+        <v>0.1034735022166796</v>
       </c>
       <c r="N4" t="n">
-        <v>1635.543597505471</v>
+        <v>0.07578784556484044</v>
       </c>
       <c r="O4" t="n">
-        <v>1321.330638180703</v>
+        <v>0.08156214916206465</v>
       </c>
       <c r="P4" t="n">
-        <v>977.0596277883957</v>
+        <v>0.06883551965130241</v>
       </c>
       <c r="Q4" t="n">
-        <v>646.370589304182</v>
+        <v>0.04444371534602051</v>
       </c>
       <c r="R4" t="n">
-        <v>373.5592540666884</v>
+        <v>0.03128733246753012</v>
       </c>
       <c r="S4" t="n">
-        <v>179.4424072253527</v>
+        <v>0.01553551744529327</v>
       </c>
       <c r="T4" t="n">
-        <v>70.28645861204309</v>
+        <v>0.02758034768190505</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>515.19472</v>
+        <v>514.7932</v>
       </c>
       <c r="B5" t="n">
-        <v>33.54087601016531</v>
+        <v>0.04057294943959843</v>
       </c>
       <c r="C5" t="n">
-        <v>55.11492096921103</v>
+        <v>0.03772463496886391</v>
       </c>
       <c r="D5" t="n">
-        <v>86.70241889717992</v>
+        <v>0.05571715068492731</v>
       </c>
       <c r="E5" t="n">
-        <v>131.2555527601817</v>
+        <v>0.06705811783667881</v>
       </c>
       <c r="F5" t="n">
-        <v>182.8129599793673</v>
+        <v>0.06230535288382382</v>
       </c>
       <c r="G5" t="n">
-        <v>234.797351163833</v>
+        <v>0.08227725896459087</v>
       </c>
       <c r="H5" t="n">
-        <v>284.8483691584034</v>
+        <v>0.1064309961572594</v>
       </c>
       <c r="I5" t="n">
-        <v>331.7502126041914</v>
+        <v>0.08700836281799737</v>
       </c>
       <c r="J5" t="n">
-        <v>361.2878488426022</v>
+        <v>0.1048432471161636</v>
       </c>
       <c r="K5" t="n">
-        <v>371.5078604813737</v>
+        <v>0.1263840725208943</v>
       </c>
       <c r="L5" t="n">
-        <v>364.2970009382957</v>
+        <v>0.1244026471161621</v>
       </c>
       <c r="M5" t="n">
-        <v>348.2078599272111</v>
+        <v>0.1184641597651574</v>
       </c>
       <c r="N5" t="n">
-        <v>317.414989420521</v>
+        <v>0.1054444694751744</v>
       </c>
       <c r="O5" t="n">
-        <v>275.0558603777755</v>
+        <v>0.08618681752712394</v>
       </c>
       <c r="P5" t="n">
-        <v>218.1510430437585</v>
+        <v>0.07379971397259719</v>
       </c>
       <c r="Q5" t="n">
-        <v>157.5557132325692</v>
+        <v>0.06148619777974987</v>
       </c>
       <c r="R5" t="n">
-        <v>99.703511528486</v>
+        <v>0.04881404172210985</v>
       </c>
       <c r="S5" t="n">
-        <v>55.73409872367706</v>
+        <v>0.04513509877245702</v>
       </c>
       <c r="T5" t="n">
-        <v>27.29912554481753</v>
+        <v>0.03155248631915793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>515.2894700000001</v>
+        <v>514.8895</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.87904060959318</v>
+        <v>0.02678185632449541</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.206236036824766</v>
+        <v>0.02090237623198564</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1432478822893087</v>
+        <v>0.03417031910335985</v>
       </c>
       <c r="E6" t="n">
-        <v>4.91393886923853</v>
+        <v>0.07863539720333867</v>
       </c>
       <c r="F6" t="n">
-        <v>12.83451559039491</v>
+        <v>0.0848905934388835</v>
       </c>
       <c r="G6" t="n">
-        <v>23.79952923232909</v>
+        <v>0.09999014867104747</v>
       </c>
       <c r="H6" t="n">
-        <v>34.26409467527549</v>
+        <v>0.119573428713743</v>
       </c>
       <c r="I6" t="n">
-        <v>42.78563749762619</v>
+        <v>0.1111416073296483</v>
       </c>
       <c r="J6" t="n">
-        <v>48.94431909410113</v>
+        <v>0.1287061564205561</v>
       </c>
       <c r="K6" t="n">
-        <v>49.9490845875561</v>
+        <v>0.1357691573883548</v>
       </c>
       <c r="L6" t="n">
-        <v>46.17140348738564</v>
+        <v>0.1325096693328489</v>
       </c>
       <c r="M6" t="n">
-        <v>39.60034448117814</v>
+        <v>0.1170481524568494</v>
       </c>
       <c r="N6" t="n">
-        <v>33.0811769309449</v>
+        <v>0.09775373244617661</v>
       </c>
       <c r="O6" t="n">
-        <v>25.00104495934754</v>
+        <v>0.1033212779220702</v>
       </c>
       <c r="P6" t="n">
-        <v>17.18405764625303</v>
+        <v>0.08466958035936027</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.574110651576644</v>
+        <v>0.05347343462017033</v>
       </c>
       <c r="R6" t="n">
-        <v>3.280087329073857</v>
+        <v>0.04456998626578566</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3543645516187205</v>
+        <v>0.0532683829923461</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.320725908223081</v>
+        <v>0.03870848276107162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>515.3842</v>
+        <v>514.9859</v>
       </c>
       <c r="B7" t="n">
-        <v>1.135555004152329</v>
+        <v>0.006408958092865576</v>
       </c>
       <c r="C7" t="n">
-        <v>3.197414192362372</v>
+        <v>0.03060351193737539</v>
       </c>
       <c r="D7" t="n">
-        <v>6.298247910953368</v>
+        <v>0.04641665142145179</v>
       </c>
       <c r="E7" t="n">
-        <v>9.87017801636892</v>
+        <v>0.06328862702721463</v>
       </c>
       <c r="F7" t="n">
-        <v>13.73608728581745</v>
+        <v>0.1268025718128351</v>
       </c>
       <c r="G7" t="n">
-        <v>18.16091907988385</v>
+        <v>0.129487363515379</v>
       </c>
       <c r="H7" t="n">
-        <v>21.9660438408764</v>
+        <v>0.1197652199822006</v>
       </c>
       <c r="I7" t="n">
-        <v>24.25895132099721</v>
+        <v>0.1354167081373319</v>
       </c>
       <c r="J7" t="n">
-        <v>24.78231647424796</v>
+        <v>0.1572132197544802</v>
       </c>
       <c r="K7" t="n">
-        <v>24.13072720210462</v>
+        <v>0.164443668977038</v>
       </c>
       <c r="L7" t="n">
-        <v>21.4827271236814</v>
+        <v>0.1477741779469734</v>
       </c>
       <c r="M7" t="n">
-        <v>18.27918901998041</v>
+        <v>0.1339913080163571</v>
       </c>
       <c r="N7" t="n">
-        <v>15.43384425404108</v>
+        <v>0.1220688885820936</v>
       </c>
       <c r="O7" t="n">
-        <v>12.09616333054173</v>
+        <v>0.08033212727272125</v>
       </c>
       <c r="P7" t="n">
-        <v>8.873176383519368</v>
+        <v>0.04894464686710182</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.857258545673806</v>
+        <v>0.03430501638854039</v>
       </c>
       <c r="R7" t="n">
-        <v>3.907538513144994</v>
+        <v>0.02342769457391747</v>
       </c>
       <c r="S7" t="n">
-        <v>2.473585938510466</v>
+        <v>0.01880259459170825</v>
       </c>
       <c r="T7" t="n">
-        <v>1.285661035517669</v>
+        <v>0.01560767115459766</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>515.47894</v>
+        <v>515.0823</v>
       </c>
       <c r="B8" t="n">
-        <v>1.209615984804993</v>
+        <v>0.04788760355808215</v>
       </c>
       <c r="C8" t="n">
-        <v>1.549573540344215</v>
+        <v>0.07275578575341923</v>
       </c>
       <c r="D8" t="n">
-        <v>2.545729151110853</v>
+        <v>0.1744546106813604</v>
       </c>
       <c r="E8" t="n">
-        <v>3.951486689690981</v>
+        <v>0.3341580076071621</v>
       </c>
       <c r="F8" t="n">
-        <v>5.603227821317624</v>
+        <v>0.4215104074079029</v>
       </c>
       <c r="G8" t="n">
-        <v>6.889729630365473</v>
+        <v>0.4784502836292115</v>
       </c>
       <c r="H8" t="n">
-        <v>8.418038215579486</v>
+        <v>0.527151806162565</v>
       </c>
       <c r="I8" t="n">
-        <v>10.06513723979669</v>
+        <v>0.5616653419177658</v>
       </c>
       <c r="J8" t="n">
-        <v>11.10690702842374</v>
+        <v>0.5612376776729696</v>
       </c>
       <c r="K8" t="n">
-        <v>11.21910781484931</v>
+        <v>0.4701663461803595</v>
       </c>
       <c r="L8" t="n">
-        <v>10.45592925807757</v>
+        <v>0.3538375315281713</v>
       </c>
       <c r="M8" t="n">
-        <v>9.432108493341746</v>
+        <v>0.2922886343639702</v>
       </c>
       <c r="N8" t="n">
-        <v>7.618121339521275</v>
+        <v>0.2205880523678895</v>
       </c>
       <c r="O8" t="n">
-        <v>5.712690853976025</v>
+        <v>0.1508651976516521</v>
       </c>
       <c r="P8" t="n">
-        <v>3.852437722904174</v>
+        <v>0.1211867885998841</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.608176244568031</v>
+        <v>0.06556606761785669</v>
       </c>
       <c r="R8" t="n">
-        <v>1.435354531708073</v>
+        <v>0.03445079390855463</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5901248368452088</v>
+        <v>0.03558660369329032</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3282997700466189</v>
+        <v>0.02092812699519502</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>515.57366</v>
+        <v>515.1786</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1296941118225361</v>
+        <v>1.12081651807855</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1851708632497856</v>
+        <v>2.699864136153507</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5584703433200073</v>
+        <v>5.126424807549872</v>
       </c>
       <c r="E9" t="n">
-        <v>1.464755644314121</v>
+        <v>8.135554047243652</v>
       </c>
       <c r="F9" t="n">
-        <v>2.631647759502965</v>
+        <v>10.38240395038527</v>
       </c>
       <c r="G9" t="n">
-        <v>3.803215223309122</v>
+        <v>11.35774803343092</v>
       </c>
       <c r="H9" t="n">
-        <v>4.751822772113981</v>
+        <v>11.10232418139038</v>
       </c>
       <c r="I9" t="n">
-        <v>6.285963570210944</v>
+        <v>9.074659129414014</v>
       </c>
       <c r="J9" t="n">
-        <v>7.630430700235451</v>
+        <v>6.589465244105535</v>
       </c>
       <c r="K9" t="n">
-        <v>8.063934239561121</v>
+        <v>4.907710443009773</v>
       </c>
       <c r="L9" t="n">
-        <v>7.655616212078352</v>
+        <v>3.779632151317987</v>
       </c>
       <c r="M9" t="n">
-        <v>6.682606461043768</v>
+        <v>2.970900709624399</v>
       </c>
       <c r="N9" t="n">
-        <v>5.150655792703795</v>
+        <v>2.04317115391552</v>
       </c>
       <c r="O9" t="n">
-        <v>3.770897574500202</v>
+        <v>1.282020259974997</v>
       </c>
       <c r="P9" t="n">
-        <v>2.700526065889048</v>
+        <v>0.8571321755914675</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.788884064361279</v>
+        <v>0.4796130062123818</v>
       </c>
       <c r="R9" t="n">
-        <v>1.135285229170351</v>
+        <v>0.199350862899825</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5486569149997491</v>
+        <v>0.1000227150613695</v>
       </c>
       <c r="T9" t="n">
-        <v>0.318665840366791</v>
+        <v>0.04793929532111366</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>515.275</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.219618317523333</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.278307134331349</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16.30859599950064</v>
+      </c>
+      <c r="E10" t="n">
+        <v>27.64352771817618</v>
+      </c>
+      <c r="F10" t="n">
+        <v>39.34872170743699</v>
+      </c>
+      <c r="G10" t="n">
+        <v>49.97469830960663</v>
+      </c>
+      <c r="H10" t="n">
+        <v>60.80348575230997</v>
+      </c>
+      <c r="I10" t="n">
+        <v>68.37751189498151</v>
+      </c>
+      <c r="J10" t="n">
+        <v>71.14695834179859</v>
+      </c>
+      <c r="K10" t="n">
+        <v>66.36293926079557</v>
+      </c>
+      <c r="L10" t="n">
+        <v>53.12688166026286</v>
+      </c>
+      <c r="M10" t="n">
+        <v>35.05018539070365</v>
+      </c>
+      <c r="N10" t="n">
+        <v>18.98328225139157</v>
+      </c>
+      <c r="O10" t="n">
+        <v>10.43191788514421</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.55378341814582</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.74851046545434</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.295356491321732</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6746548637039167</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.2243451666393713</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>515.3714</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4228804624514895</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.044787355957937</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.273973112172042</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.828729193531038</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8.165225606247386</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.05621130796565</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16.65900558342519</v>
+      </c>
+      <c r="I11" t="n">
+        <v>21.38436778102668</v>
+      </c>
+      <c r="J11" t="n">
+        <v>26.42892250873311</v>
+      </c>
+      <c r="K11" t="n">
+        <v>33.11222473628643</v>
+      </c>
+      <c r="L11" t="n">
+        <v>40.74504525796527</v>
+      </c>
+      <c r="M11" t="n">
+        <v>47.4001135516207</v>
+      </c>
+      <c r="N11" t="n">
+        <v>49.66812965624249</v>
+      </c>
+      <c r="O11" t="n">
+        <v>43.70712081338935</v>
+      </c>
+      <c r="P11" t="n">
+        <v>30.98457433821507</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>16.54518864770557</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5.574195922034811</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.848250684319379</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.5050469353566608</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>515.4677</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.02671215469845025</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.06083942620885509</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1391653170467784</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3315850865753177</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6013700268848508</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.071440019434184</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.825833054943823</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.088657461270005</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.9295281874894</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.678185247393126</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.16957174323353</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11.59576987264101</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12.12490751005068</v>
+      </c>
+      <c r="O12" t="n">
+        <v>12.37131578853492</v>
+      </c>
+      <c r="P12" t="n">
+        <v>11.90901535249154</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>10.68809686405186</v>
+      </c>
+      <c r="R12" t="n">
+        <v>10.33553403570817</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7.935972129257542</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.20773027650572</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>515.564</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.03355634475715814</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.04946903018679578</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.06062869273082627</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.07144518178971178</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.110087455570175</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1672862765415281</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2222499653442281</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3219886082405025</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.4639389379398335</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7307117571107796</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.353158990357486</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.766539137562503</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.490042897398701</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5.465635695356287</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5.123487160220216</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.57248061572647</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.432816783127374</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.728035951211399</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.9180697825012654</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>515.6604</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.02963187636363412</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0213885890909075</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.03846982961038673</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.07802263688311101</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1110142929870047</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1266622898701203</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1403086483116778</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1748291594805063</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.1853208290908951</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.1854115401529838</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2037080312115129</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2562292810602904</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3832973991246823</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.7833260024123235</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.393654621504965</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.525401043792804</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.328983960270315</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.9684089954598096</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.5029365143710707</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>515.7567</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.01320086045899208</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0271993117737037</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.03144268722291174</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.08321317297277439</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1142512833374758</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1126086827539499</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1581614579683211</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1676100073225279</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1700097914819299</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.1865743455185769</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1699502085892062</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.165736035787214</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1456916028962708</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.1325558990570973</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.1462964128233301</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.163378714243005</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3252434187653198</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3992707634086161</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.2831013875253301</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>515.853</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.01583936626222973</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.01817208239814844</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.02824195268457358</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.03604653578366569</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.07490295043585987</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.1082453449065921</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1107674888738575</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1273923480875193</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1425631351503184</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1559596334673428</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1706818895071923</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.166455409151384</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1299186469311413</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.1044796527948685</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.09600087980073996</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.06189024867460841</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.03858755760184732</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.0379125952179299</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.0350183826721198</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>515.9493</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.02136748690980093</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03863239916028886</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.0560204091585085</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.05342774793096914</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0704508972567106</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.08442186013875901</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1142781060380629</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1215094951859008</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.1239637458032285</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.1388777863582888</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1368897832841029</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1495521546201631</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1304478819142403</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.1148170814516904</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.1030799083365871</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.06688011911047355</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.04579268659668754</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.04232720143034728</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.02975640250489014</v>
       </c>
     </row>
   </sheetData>
